--- a/public/dopamichi-itinerary-template.xlsx
+++ b/public/dopamichi-itinerary-template.xlsx
@@ -3341,7 +3341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
     <col min="2" max="2" width="90.83203125" customWidth="1"/>
@@ -3408,36 +3408,36 @@
         <v>Breakfast / Lunch / Dinner</v>
       </c>
       <c r="B8" t="str">
-        <v>The three meal slots.</v>
+        <v>The three core meal slots.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Timeline</v>
+        <v>Brunch / Afternoon / Late night</v>
       </c>
       <c r="B9" t="str">
-        <v>The ordered activity timeline (sorted by Time).</v>
+        <v>Optional extra meals (มื้อสาย / มื้อบ่าย / มื้อดึก) — add a row with this Slot only when you need it.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Accommodation</v>
+        <v>Timeline</v>
       </c>
       <c r="B10" t="str">
-        <v>Where you stay that night.</v>
+        <v>The ordered activity timeline (sorted by Time).</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Accommodation</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Where you stay that night.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>COLUMN: Category — root prefix decides how it renders</v>
+        <v/>
       </c>
       <c r="B12" t="str">
         <v/>
@@ -3445,55 +3445,55 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>log.*</v>
+        <v>COLUMN: Category — root prefix decides how it renders</v>
       </c>
       <c r="B13" t="str">
-        <v>Logistics node → compact transport/connector row in the timeline (train, bus, walk). e.g. log.rail.jr, log.bus.city, log.walk</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>live.*</v>
+        <v>log.*</v>
       </c>
       <c r="B14" t="str">
-        <v>Accommodation. e.g. live.stay.hotel</v>
+        <v>Logistics node → compact transport/connector row in the timeline (train, bus, walk). e.g. log.rail.jr, log.bus.city, log.walk</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>food.*</v>
+        <v>live.*</v>
       </c>
       <c r="B15" t="str">
-        <v>Meal / café / dessert. e.g. food.dine.ramen, food.cafe</v>
+        <v>Accommodation. e.g. live.stay.hotel</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>exp.*</v>
+        <v>food.*</v>
       </c>
       <c r="B16" t="str">
-        <v>Sightseeing / activity. e.g. exp.land.temple, exp.act.boat</v>
+        <v>Meal / café / dessert. e.g. food.dine.ramen, food.cafe</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>shop.*</v>
+        <v>exp.*</v>
       </c>
       <c r="B17" t="str">
-        <v>Shopping. e.g. shop.tea, shop.mall</v>
+        <v>Sightseeing / activity. e.g. exp.land.temple, exp.act.boat</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>shop.*</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Shopping. e.g. shop.tea, shop.mall</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>COLUMN: Priority — timeline nodes only</v>
+        <v/>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -3501,23 +3501,23 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Must / Recommend / Optional</v>
+        <v>COLUMN: Priority — timeline nodes only</v>
       </c>
       <c r="B20" t="str">
-        <v>The must-do / recommended / optional badge. Blank = Optional.</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Must / Recommend / Optional</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>The must-do / recommended / optional badge. Blank = Optional.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>COLUMN: Choice group + Default? — pick-one options (meals &amp; accommodation)</v>
+        <v/>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -3525,31 +3525,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choice group</v>
+        <v>COLUMN: Choice group + Default? — pick-one options (meals &amp; accommodation)</v>
       </c>
       <c r="B23" t="str">
-        <v>Give 2+ rows in the SAME day + slot the same label (e.g. "dinner") to turn them into a pick-one choice.</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Default?</v>
+        <v>Choice group</v>
       </c>
       <c r="B24" t="str">
-        <v>Put Y on the option that should be pre-selected.</v>
+        <v>Give 2+ rows in the SAME day + slot the same label (e.g. "dinner") to turn them into a pick-one choice.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Default?</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Put Y on the option that should be pre-selected.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>OTHER COLUMNS</v>
+        <v/>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -3557,23 +3557,31 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Time</v>
+        <v>OTHER COLUMNS</v>
       </c>
       <c r="B27" t="str">
-        <v>HH:MM (24h). Name (EN) / (TH), Emoji, Cost (e.g. ¥1,500 / Free), Duration (e.g. 1.5h), Notes, Map URL — all optional per node.</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>Time</v>
+      </c>
+      <c r="B28" t="str">
+        <v>HH:MM (24h). Name (EN) / (TH), Emoji, Cost (e.g. ¥1,500 / Free), Duration (e.g. 1.5h), Notes, Map URL — all optional per node.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>Free</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B29" t="str">
         <v>Put Y to mark the whole day as a free/open day.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B29"/>
   </ignoredErrors>
 </worksheet>
 </file>